--- a/public/downloads/product-scoring.xlsx
+++ b/public/downloads/product-scoring.xlsx
@@ -47,7 +47,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="005A5A5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,15 +107,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -505,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Score each candidate 0–10. Score × Weight = weighted score. Sum → final. Fill rows from row 5.</t>
+          <t>Score each candidate 0–10. Yellow cells = your scores. Gray cell = weighted total. See 'How to score' for what each score means.</t>
         </is>
       </c>
     </row>
@@ -733,36 +736,71 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="J10" s="10">
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="9">
         <f>IFERROR(B10*B4,0)+IFERROR(C10*C4,0)+IFERROR(D10*D4,0)+IFERROR(E10*E4,0)+IFERROR(F10*F4,0)+IFERROR(G10*G4,0)+IFERROR(H10*H4,0)+IFERROR(I10*I4,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="J11" s="10">
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="9">
         <f>IFERROR(B11*B4,0)+IFERROR(C11*C4,0)+IFERROR(D11*D4,0)+IFERROR(E11*E4,0)+IFERROR(F11*F4,0)+IFERROR(G11*G4,0)+IFERROR(H11*H4,0)+IFERROR(I11*I4,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="J12" s="10">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="9">
         <f>IFERROR(B12*B4,0)+IFERROR(C12*C4,0)+IFERROR(D12*D4,0)+IFERROR(E12*E4,0)+IFERROR(F12*F4,0)+IFERROR(G12*G4,0)+IFERROR(H12*H4,0)+IFERROR(I12*I4,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="J13" s="10">
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="9">
         <f>IFERROR(B13*B4,0)+IFERROR(C13*C4,0)+IFERROR(D13*D4,0)+IFERROR(E13*E4,0)+IFERROR(F13*F4,0)+IFERROR(G13*G4,0)+IFERROR(H13*H4,0)+IFERROR(I13*I4,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="J14" s="10">
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="9">
         <f>IFERROR(B14*B4,0)+IFERROR(C14*C4,0)+IFERROR(D14*D4,0)+IFERROR(E14*E4,0)+IFERROR(F14*F4,0)+IFERROR(G14*G4,0)+IFERROR(H14*H4,0)+IFERROR(I14*I4,0)</f>
         <v/>
       </c>
@@ -825,10 +863,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B18:I18"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B19:I19"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
